--- a/五一特别活动.xlsx
+++ b/五一特别活动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="25300" windowHeight="11300" activeTab="1"/>
+    <workbookView windowWidth="25300" windowHeight="11900"/>
   </bookViews>
   <sheets>
     <sheet name="活动积分记录" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>姓名</t>
   </si>
@@ -42,118 +42,10 @@
     <t>积分变化</t>
   </si>
   <si>
-    <t>Alvin</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>完成任务A</t>
-  </si>
-  <si>
-    <t>煮鱼</t>
-  </si>
-  <si>
-    <t>完成任务B</t>
-  </si>
-  <si>
-    <t>Tracy</t>
-  </si>
-  <si>
-    <t>参与讨论</t>
-  </si>
-  <si>
-    <t>外国公主</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>分享资源</t>
-  </si>
-  <si>
-    <t>Moon</t>
-  </si>
-  <si>
-    <t>Shortcuts 入门</t>
-  </si>
-  <si>
-    <t>花果山小母猴</t>
-  </si>
-  <si>
-    <t>Good Idea</t>
-  </si>
-  <si>
-    <t>Bryan</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>认真学习 Town Hall</t>
-  </si>
-  <si>
-    <t>幼儿园高材生</t>
-  </si>
-  <si>
-    <t>Peer Tips</t>
-  </si>
-  <si>
-    <t>Julia</t>
-  </si>
-  <si>
-    <t>新用户注册</t>
-  </si>
-  <si>
-    <t>8low8lowme</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>完成任务C</t>
-  </si>
-  <si>
-    <t>Lucia</t>
-  </si>
-  <si>
-    <t>泡泡</t>
-  </si>
-  <si>
-    <t>Ya</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>新来的同事</t>
-  </si>
-  <si>
-    <t>完成入职培训</t>
-  </si>
-  <si>
-    <t>测试用户</t>
-  </si>
-  <si>
-    <t>测试积分</t>
-  </si>
-  <si>
     <t>兑换物品</t>
   </si>
   <si>
     <t>消耗积分</t>
-  </si>
-  <si>
-    <t>咖啡券</t>
-  </si>
-  <si>
-    <t>零食大礼包</t>
-  </si>
-  <si>
-    <t>笔记本</t>
-  </si>
-  <si>
-    <t>钥匙扣</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1051,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.8303571428571" customWidth="1"/>
@@ -1182,221 +1074,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D16" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1404,8 +1086,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.8303571428571" customWidth="1"/>
     <col min="2" max="2" width="12.8303571428571" customWidth="1"/>
@@ -1421,65 +1103,9 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5">
         <v>5</v>
       </c>
     </row>
@@ -1487,7 +1113,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D2 A3:C3 A4:D5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/五一特别活动.xlsx
+++ b/五一特别活动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="25300" windowHeight="11900"/>
+    <workbookView windowWidth="25300" windowHeight="11900" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="活动积分记录" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
   <si>
     <t>姓名</t>
   </si>
@@ -40,6 +40,39 @@
   </si>
   <si>
     <t>积分变化</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>测试</t>
+  </si>
+  <si>
+    <t>Daisy Lu</t>
+  </si>
+  <si>
+    <t>Danni</t>
+  </si>
+  <si>
+    <t>Dido</t>
+  </si>
+  <si>
+    <t>Edward</t>
+  </si>
+  <si>
+    <t>Laughing</t>
+  </si>
+  <si>
+    <t>Patrick</t>
+  </si>
+  <si>
+    <t>Sally</t>
+  </si>
+  <si>
+    <t>Alvin</t>
+  </si>
+  <si>
+    <t>Tracy</t>
   </si>
   <si>
     <t>兑换物品</t>
@@ -666,8 +699,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1051,7 +1085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.8303571428571" customWidth="1"/>
@@ -1072,6 +1106,146 @@
       </c>
       <c r="D1" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1086,8 +1260,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelCol="3"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.8303571428571" customWidth="1"/>
     <col min="2" max="2" width="12.8303571428571" customWidth="1"/>
@@ -1103,10 +1277,54 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/五一特别活动.xlsx
+++ b/五一特别活动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="25300" windowHeight="11900" activeTab="1"/>
+    <workbookView windowWidth="25300" windowHeight="11900"/>
   </bookViews>
   <sheets>
     <sheet name="活动积分记录" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>姓名</t>
   </si>
@@ -40,39 +40,6 @@
   </si>
   <si>
     <t>积分变化</t>
-  </si>
-  <si>
-    <t>Angela</t>
-  </si>
-  <si>
-    <t>测试</t>
-  </si>
-  <si>
-    <t>Daisy Lu</t>
-  </si>
-  <si>
-    <t>Danni</t>
-  </si>
-  <si>
-    <t>Dido</t>
-  </si>
-  <si>
-    <t>Edward</t>
-  </si>
-  <si>
-    <t>Laughing</t>
-  </si>
-  <si>
-    <t>Patrick</t>
-  </si>
-  <si>
-    <t>Sally</t>
-  </si>
-  <si>
-    <t>Alvin</t>
-  </si>
-  <si>
-    <t>Tracy</t>
   </si>
   <si>
     <t>兑换物品</t>
@@ -1108,145 +1075,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1">
-        <v>46143</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11">
-        <v>30</v>
-      </c>
+    <row r="2" spans="2:2">
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1277,55 +1134,23 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1">
-        <v>46143</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1">
-        <v>46143</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1">
-        <v>46143</v>
-      </c>
-      <c r="D4">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1">
-        <v>46143</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
+    <row r="2" spans="2:2">
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
